--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_014/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_014/extracted.xlsx
@@ -280,6 +280,11 @@
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1306,17 +1311,17 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>S-duct CFD Credibility Assessment – eVTOL Inlet Option C</t>
+          <t>S-duct CFD Credibility Assessment – AIP Distortion and Recovery</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Steady RANS CFD of S-duct inlet for AIP total-pressure recovery and distortion prediction at M=0.60</t>
+          <t>Steady RANS CFD prediction of AIP total-pressure recovery and swirl distortion for eVTOL inlet Option C S-duct downselect</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Ansys Fluent k-omega SST simulations of an eVTOL S-duct inlet (Option C geometry) used to predict area-averaged AIP pressure recovery, circumferential total-pressure distortion (DPCPavg), and swirl angle at M=0.60, Re_D=5.0e6. Results are used to downselect the duct variant for Q3 wind-tunnel screening and to guide AIP rake placement. Steady RANS is acknowledged as acceptable for ranking and preliminary design but not for final certification.</t>
+          <t>Ansys Fluent k-omega SST simulations of a diffusing S-duct at M=0.60, Re_D=5.0e6 are used to predict area-averaged total-pressure recovery and circumferential distortion (DPCPavg) at the Aerodynamic Interface Plane (AIP) to support Q3 wind-tunnel screening and variant downselect. The model is not intended for final certification; it supports a preliminary design review gate.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1354,9 +1359,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1475,7 +1480,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>IPT Gate Acceptance Criteria – AIP Recovery and Swirl</t>
+          <t>IPT AIP Recovery and Swirl Acceptance Criteria</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1485,7 +1490,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Predict AIP area-averaged pressure recovery within 2.0 percentage points of reference data and reproduce swirl orientation and lobe structure; required for Q3 wind-tunnel downselect gate</t>
+          <t>Predict AIP area-averaged total-pressure recovery within 2.0 percentage points of reference data and correctly reproduce swirl orientation and lobe structure; required for Q3 wind-tunnel downselect gate (PDR).</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1507,12 +1512,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023R1 – k-omega SST S-duct RANS Model</t>
+          <t>Ansys Fluent 2023R1 k-omega SST S-duct CFD Model</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Density-based coupled solver, second-order spatial, k-omega SST with production limiter, y+~0.8; three mesh levels (2.1M/4.8M/10.2M cells) on eVTOL inlet Option C geometry</t>
+          <t>Density-based coupled solver, second-order spatial discretization, k-omega SST with production limiter, y+≈0.8, applied to eVTOL inlet Option C geometry at M=0.60 isothermal conditions.</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1534,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>AIP plane measurements (total-pressure recovery, DPCPavg, swirl) at comparable Mach and Reynolds numbers; used as the primary validation comparator</t>
+          <t>AIP plane total-pressure recovery, DPCPavg distortion, and swirl angle measurements at comparable Mach and Reynolds numbers used as the primary validation comparator.</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1546,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Inlet Facility Survey – Turbulence Intensity and Total Conditions</t>
+          <t>Facility Inlet Boundary Condition Survey</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Prior facility survey providing inlet total conditions (Pt=101.3 kPa, Tt=300 K) and turbulence intensity (1% ±0.5%) used as model boundary condition inputs</t>
+          <t>Prior wind-tunnel facility survey providing turbulence intensity (1% ±0.5%) and inlet total conditions (Pt=101.3 kPa, Tt=300 K) used to set CFD boundary conditions.</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1988,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study – AIP Pressure Recovery and Swirl</t>
+          <t>Mesh Convergence Study – AIP Recovery and Swirl</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1998,12 +2003,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Three unstructured mesh levels (2.1M, 4.8M, 10.2M cells) assessed for convergence of AIP area-averaged recovery and separation bubble length; observed spatial order ~1.8; monotonic convergence confirmed</t>
+          <t>Three unstructured meshes (2.1M, 4.8M, 10.2M cells) were run; pressure recovery monitored at AIP, separation bubble length tracked. Monotonic convergence observed with apparent order ~1.8.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / GCI method</t>
+          <t>Richardson extrapolation and GCI analysis; grid-to-grid changes in recovery and bubble length</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2013,12 +2018,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Grid Convergence Index (GCI), assumed ratio of areas = 1.8</t>
+          <t>Grid Convergence Index (GCI), Richardson extrapolation</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>GCI on recovery at finest grid = 1.6%; recovery change coarse-to-fine = 1.9 percentage points; separation bubble length shift medium-to-fine &lt; 5% of duct centerline length</t>
+          <t>GCI on recovery at finest grid = 1.6%; recovery change coarse-to-fine = +1.9 pp; bubble length shift medium-to-fine &lt; 5% of centerline length</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2040,12 +2045,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Fine-grid SST predictions of area-averaged AIP recovery, DPCPavg, and swirl RMS compared quantitatively against Wellborn et al. diffusing S-duct measurements at comparable M and Re</t>
+          <t>Fine-grid SST predictions of area-averaged recovery, DPCPavg circumferential distortion, and swirl angle RMS compared against Wellborn et al. S-duct measurements at matched Mach and Reynolds conditions.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Wellborn et al. (NASA TM-1993-XXXX) experimental AIP measurements</t>
+          <t>Wellborn et al. NASA TM-1993-XXXX experimental AIP measurements</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2055,12 +2060,12 @@
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>Root-sum-square combination of mesh, turbulence model, TI, back-pressure, and roughness uncertainty contributors</t>
+          <t>Root-sum-square combination of mesh, turbulence model, TI, back-pressure, and roughness sensitivities</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>Recovery error 1.1% (within 2.0 pt gate); DPCPavg error within 0.02; swirl RMS error 2.3 deg; reattachment location 7% downstream of reported mean; combined recovery uncertainty ~3.2%; combined swirl uncertainty ~3.0 deg</t>
+          <t>Recovery error 1.1% (&lt; 2.0 pp threshold); DPCPavg error ≤ 0.02; swirl RMS error 2.3 deg; reattachment 7% downstream of reported mean</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2072,7 +2077,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Turbulence Model Sensitivity – Realizable k-epsilon Cross-check</t>
+          <t>Turbulence Model Sensitivity Study</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2082,12 +2087,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Realizable k-epsilon run on the same medium/fine mesh to bracket turbulence closure uncertainty; shifts in recovery and peak swirl compared to baseline SST</t>
+          <t>Realizable k-epsilon run on the same fine mesh compared to SST baseline to bracket turbulence closure uncertainty on recovery and peak swirl.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>k-omega SST baseline predictions</t>
+          <t>SST baseline predictions</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2097,12 +2102,12 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>One-at-a-time sensitivity sweep; turbulence closure uncertainty contribution isolated</t>
+          <t>One-at-a-time sensitivity sweep</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>Recovery shift -0.9 percentage points; peak swirl increase ~3 deg relative to SST; consistent with expected behavior in separated curvature flows</t>
+          <t>Recovery shift -0.9 pp; peak swirl increase ~3 deg relative to SST</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2114,7 +2119,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Numerical Code Verification – Method of Manufactured Solutions</t>
+          <t>Manufactured Solution Code Verification</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2124,7 +2129,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Baseline Ansys Fluent solver verified on two manufactured fields (isentropic vortex and source-driven channel) to confirm correct spatial order of accuracy on tetra/prism meshes</t>
+          <t>Baseline solver verified on isentropic vortex and source-driven channel manufactured fields to confirm spatial order of accuracy on tetra/prism meshes.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -2151,7 +2156,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Iterative Solver Convergence Monitoring</t>
+          <t>Iterative Solver Convergence Check</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2161,12 +2166,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Residual levels and AIP plane mass balance monitored at AIP centerline and upper-quadrant monitor points to confirm iterative convergence</t>
+          <t>Residuals and AIP mass balance monitored for all production runs to confirm iterative convergence.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Prescribed residual and mass balance targets</t>
+          <t>Residual targets and mass conservation thresholds</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2330,12 +2335,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver with documented verification and change control; version-controlled case files</t>
+          <t>Commercial solver with documented version control and reproducible case archive</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023R1 is a commercial solver with established QA processes. Case files archived under version-controlled repository (cfd/inletC/sduct/AIPv7) with tags for mesh and model variants. Journal files capture all solver options; PyFluent postprocessing script included. Double-precision runs; report template v2.3 used. No explicit mention of ISO certification or formal regression test suite beyond the MMS checks described under code verification.</t>
+          <t>Ansys Fluent 2023R1 is a commercially released, widely validated CFD solver with vendor QA processes. Cases archived under version-tagged repository (cfd/inletC/sduct/AIPv7); journal files capture all solver options; double-precision runs with report template v2.3 documented. No explicit ISO or internal SQA plan cited, but commercial release status and full archive provide adequate evidence.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2364,12 +2369,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Demonstrated correct spatial order of accuracy for the governing equations on the mesh types used</t>
+          <t>Demonstrated correct order of accuracy on representative mesh types</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Solver verified against two manufactured fields: isentropic vortex and source-driven channel. Observed spatial order 2.0 for pressure and 1.8 for velocity on the tetra/prism mesh topology used in the production runs. No anomalous behavior at Courant numbers up to 10. This constitutes quantified, problem-relevant MMS verification exceeding a basic check.</t>
+          <t>Solver verified against two manufactured solutions (isentropic vortex and source-driven channel) on tetra/prism meshes matching production runs. Observed spatial order 2.0 (pressure) and 1.8 (velocity) consistent with second-order scheme. No anomalous behavior noted up to CFL=10. Quantified and matches theoretical expectation, providing thorough code verification evidence.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2398,12 +2403,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Monotonic convergence demonstrated across mesh levels with GCI on primary QoI reported</t>
+          <t>GCI on primary QoI below acceptance threshold; monotonic convergence demonstrated</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three mesh levels (2.1M/4.8M/10.2M cells) with wall-normal first layer 6 μm and growth ≤1.2. Monotonic convergence with observed order ~1.8. GCI on AIP recovery at finest grid = 1.6%. Recovery change coarse-to-fine = 1.9 percentage points. Separation bubble length shift medium-to-fine &lt;5% duct length. Coarse mesh excluded from recommendations. Quantified uncertainty contribution from mesh = 1.6% on recovery.</t>
+          <t>Three-level mesh refinement study (2.1M/4.8M/10.2M cells) with monotonic recovery convergence, apparent order ~1.8. GCI on AIP recovery at finest grid = 1.6%. Separation bubble length shift &lt; 5% medium-to-fine. Quantified uncertainty contribution (1.6% on recovery) carried into combined UQ budget. Coarse mesh explicitly excluded from recommendations.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2432,12 +2437,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residuals and key monitor quantities reach stable, acceptably low levels; mass conservation verified</t>
+          <t>Residuals reach target levels; mass conservation satisfied</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Residuals dropped to 1e-5 at AIP centerline and upper-quadrant monitor points. Plane mass balance within 0.1%. Outlet static pressure iterated to match target mass flow rate ±0.2%. Density-based coupled solver used, second-order spatial. No evidence of oscillatory or non-convergent behavior reported.</t>
+          <t>Monitor points at AIP centerline and upper quadrant confirm residuals to 1e-5 and plane mass balance within 0.1% for all production runs. Consistent convergence behavior reported; no divergence or stall noted. Provides adequate iterative convergence evidence.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2466,12 +2471,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Model setup independently reviewable; boundary conditions verified; mesh quality documented</t>
+          <t>Independent check or documented review of boundary conditions and post-processing setup</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Journal files capture all solver options ensuring reproducibility. Case archived with version tags. AIP postprocessing script (PyFluent) included for traceability. Boundary conditions explicitly documented (Pt, Tt, TI, outlet static pressure iteration, wall thermal condition, no secondary flows). Memo is addressed to IPT Lead (A. Ruiz) implying review. No explicit independent third-party review of setup is documented; memo serves as informal record of setup rationale.</t>
+          <t>Outlet static pressure iterated to match target mass flow ±0.2%, confirming BC implementation. PyFluent AIP post-processing script included in archive enabling reproducibility. Journal files capture all solver options. Memo is addressed to IPT lead (A. Ruiz), implying review. No explicit independent third-party verification of setup documented; boundary condition derivation is traceable. Adequate but not thorough evidence.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2500,12 +2505,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equation and turbulence model selection justified; known limitations documented</t>
+          <t>Turbulence model selection justified; known limitations documented</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>k-omega SST with production limiter selected and justified for separated curvature flows. Realizable k-epsilon cross-check performed as model form sensitivity bracket. Steady RANS limitation explicitly documented: acceptable for ranking and preliminary AIP rake placement, not for final certification. Short URANS probe (0.5 ms flow time) performed showing 5-10% fluctuation in separation bubble but negligible shift in mean recovery, partially bounding unsteadiness not captured by RANS. Known omissions (thermal coupling, inlet lip bleed, upstream propulsor effects, discrete roughness) documented.</t>
+          <t>k-omega SST with production limiter selected and justified for separated curvature-dominated flows. Realizable k-epsilon cross-check bounds model-form uncertainty (0.9 pp recovery, ~3 deg swirl). Steady RANS limitation explicitly documented: acceptable for ranking and preliminary rake placement, not for final certification. URANS probe reveals 5-10% fluctuation in bubble size. Known omissions (thermal coupling, lip bleed, propulsor effects) enumerated. Adequate physics justification with limitations clearly stated.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2534,12 +2539,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Boundary conditions traceable to measurements; input uncertainty characterized</t>
+          <t>Inlet boundary conditions traceable to measurements; key inputs uncertainty-characterized</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Inlet total conditions (Pt=101.3 kPa, Tt=300 K) derived from tunnel plan. Turbulence intensity from prior facility survey (1% ±0.5%). Outlet static pressure iterated to match target mass flow rate ±0.2%. Roughness modeled as k_s=10 μm equivalent sandgrain. Geometry 1:1 with Option C CAD including corner fillets. Sensitivity of QoIs to TI (±0.3 points on recovery) and roughness (±0.5 points for 0-25 μm) and back-pressure (±0.6 points) individually quantified. Updated facility survey (TI=3%) not yet incorporated — flagged as action item.</t>
+          <t>Inlet total conditions (Pt=101.3 kPa, Tt=300 K) from tunnel plan; TI=1%±0.5% from prior facility survey. Roughness modeled as k_s=10 μm equivalent sandgrain. Outlet back-pressure iterated to match mass flow ±0.2%. TI and roughness sensitivity sweeps performed (0.5–5% TI; 0–25 μm roughness). Geometry 1:1 with Option C CAD including corner fillets. Wall thermal condition held adiabatic with rationale. Input uncertainty quantified and propagated.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2568,12 +2573,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Reference experimental data is adequately described and representative</t>
+          <t>Validation dataset is adequately described with sufficient measurement points</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Wellborn et al. NASA TM-1993 diffusing S-duct dataset used as comparator. Dataset is a published NASA technical memorandum at comparable Mach and Reynolds. Described as having minimal unsteady content. No information on number of repeat test articles, statistical characterization of measurements, or production-representativeness relative to eVTOL Option C geometry provided in the memo. Single archival dataset used.</t>
+          <t>Wellborn et al. NASA TM-1993-XXXX provides the experimental comparator. The memo references the dataset but does not detail specimen count, rake density, or statistical characterization of measurement repeatability. The dataset is an established NASA reference; however, sample/replication information is not reported in this document. Basic evidence with acknowledged gaps in sample characterization.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2602,12 +2607,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Experimental measurement conditions and uncertainties adequately described</t>
+          <t>Experimental conditions documented with measurement uncertainty</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Wellborn et al. conditions described as comparable Mach and Reynolds to the simulation operating point. No detailed description of instrument calibration, measurement uncertainty bounds, or controlled environment specifics from the reference experiment is provided in the memo. The memo relies on published NASA data without restating experimental uncertainty bands.</t>
+          <t>Wellborn et al. conditions described as comparable Mach and Reynolds; unsteady content noted as minimal in their setup. No explicit instrument calibration records, controlled environment specifications, or measurement uncertainty bounds from the experimental dataset are cited in this memo. Facility survey provides TI with ±0.5% uncertainty. Test condition documentation is limited to what is available from the external reference.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2632,16 +2637,16 @@
         <v>3</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model inputs explicitly matched to experimental conditions with uncertainty propagation</t>
+          <t>CFD boundary conditions demonstrably matched to experimental operating conditions</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Simulation operating point (M=0.60, Re_D=5.0e6, TI=1%) stated as comparable to Wellborn et al. conditions. Inlet total conditions taken from tunnel plan rather than from the Wellborn experiment directly. No formal table comparing simulation inputs to Wellborn experimental conditions parameter-by-parameter is provided. Uncertainty in TI (±0.5%) and its effect on QoIs quantified but not cross-referenced to Wellborn test conditions. Some gap in formal input equivalency documentation between model and validation experiment.</t>
+          <t>Mach and Reynolds numbers matched to Wellborn et al. reference conditions. Inlet total conditions derived from tunnel plan; TI from facility survey aligned to reference setup. Outlet back-pressure iterated to match mass flow. Sensitivity to TI mismatch (±0.5%) quantified as ±0.3 pp on recovery. No upstream swirl imposed consistent with Wellborn setup. Adequate parameter matching with uncertainty propagation for key inputs.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2670,12 +2675,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of primary QoIs to experimental data with uncertainty bands; meets IPT gate criteria</t>
+          <t>Quantitative error metrics reported for primary QoIs against experimental data; uncertainty bands provided</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Three QoIs compared quantitatively: area-averaged AIP recovery error 1.1% (gate ≤2.0 pt, passed); DPCPavg within 0.02; swirl RMS error 2.3 deg. Reattachment location 7% downstream of reported mean. Combined RSS uncertainty on recovery ~3.2% and swirl ~3.0 deg reported. One-at-a-time sensitivity sweeps performed for five uncertainty contributors. Turbulence model cross-check provides additional comparison point. IPT gate criteria explicitly assessed as met for medium and fine grids.</t>
+          <t>Three QoIs compared: area-averaged recovery error 1.1% (vs. 2.0 pp threshold), DPCPavg within 0.02, swirl RMS error 2.3 deg. Reattachment location compared (7% downstream shift). Combined RSS uncertainty on recovery ≈3.2%, on swirl ≈3.0 deg reported. Turbulence model cross-check provides additional comparison point. Multiple metrics and uncertainty bands provided; limited to one reference dataset and one operating point.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2700,16 +2705,16 @@
         <v>3</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs directly measure the performance quantities required for the downselect decision</t>
+          <t>QoIs directly measure the performance criteria required by the IPT gate decision</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>QoIs (AIP area-averaged total-pressure recovery, DPCPavg, swirl RMS) are exactly the quantities specified in the IPT gate acceptance criteria and are directly relevant to inlet aerodynamic performance for eVTOL propulsion system integration. These quantities are measurable both computationally (AIP plane postprocessing) and experimentally (AIP rake). QoIs also directly support AIP rake placement planning for the wind-tunnel article.</t>
+          <t>AIP area-averaged total-pressure recovery and DPCPavg distortion are the exact metrics specified in the IPT acceptance criteria for the downselect gate. Swirl angle and lobe structure directly inform rake placement decisions. All QoIs are measurable both computationally and experimentally. The connection between model outputs and the decision is direct and explicit.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2738,12 +2743,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions sufficiently match COU operating envelope and geometry</t>
+          <t>Validation conditions match COU geometry, operating regime, and physics sufficiently to support the decision</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation against Wellborn et al. diffusing S-duct at comparable M and Re provides relevant physics regime coverage. However, the Wellborn geometry is not the eVTOL Option C geometry — it is a generic diffusing S-duct used as an analog. Known gaps: thermal coupling excluded, inlet lip bleed excluded, upstream propulsor effects excluded, no upstream swirl imposed. TI used (1%) may not match updated facility survey (3% flagged as action item). Validation is adequate for downselect ranking but explicitly scoped as not sufficient for final certification. These are documented limitations, not undisclosed gaps.</t>
+          <t>Validation against Wellborn et al. at comparable Mach and Reynolds is relevant but not identical to the eVTOL Option C geometry. The Wellborn duct is a generic diffusing S-duct, not the specific Option C design. Operating point coverage is limited to a single Mach number (M=0.60). Thermal coupling, lip bleed, and upstream propulsor effects present in the actual COU are excluded. Steady RANS limitation documented for certification but accepted for this gate. Known gap between validation geometry and production geometry reduces applicability confidence.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2928,7 +2933,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The S-duct CFD model meets the stated IPT gate acceptance criteria: area-averaged AIP recovery error of 1.1% is within the 2.0 percentage point requirement, DPCPavg is within 0.02, and swirl lobe structure is reproduced on the medium and fine grids. A mesh convergence study with GCI=1.6% and MMS-based code verification with observed order ~1.8-2.0 provide adequate numerical credibility. Combined RSS uncertainty of ~3.2% on recovery and ~3.0 deg on swirl are quantified and bounded. The model is accepted for the specific COU of Q3 wind-tunnel variant downselect and AIP rake placement using fine-grid SST results. Conditions carried forward: (1) steady RANS results are not acceptable for final certification; (2) the coarse mesh is excluded; (3) a TI=3% run is required before PDR to align with the updated facility survey; (4) local refinement in the first-bend upper corner is recommended before final rake layout; (5) unsteadiness characterization via fine-grid URANS should be completed if schedule permits.</t>
+          <t>The fine-grid SST CFD model meets both IPT acceptance criteria: AIP recovery error of 1.1% is within the 2.0 percentage-point threshold and swirl orientation and lobe structure are reproduced. Combined RSS uncertainty on recovery (3.2%) and swirl (3.0 deg) are bounded and carried forward. Mesh convergence (GCI 1.6%), iterative convergence (residuals to 1e-5, mass balance 0.1%), manufactured-solution code verification (order 2.0/1.8), and turbulence model sensitivity are all satisfactory. Acceptance is granted for the stated scope: variant downselect, preliminary AIP rake placement, and wind-tunnel article fabrication support. Conditions noted: (1) coarse mesh excluded from use; (2) steady RANS not acceptable for final certification; (3) TI=3% run to be added before PDR per updated facility survey; (4) local refinement in first-bend upper corner targeted; (5) thermal coupling, lip bleed, and propulsor effects deferred to later phases.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2938,7 +2943,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>J. Park (memo author); A. Ruiz (IPT Lead, addressee)</t>
+          <t>J. Park</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
